--- a/data/hm.xlsx
+++ b/data/hm.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39EE3357-B0D7-4E22-8C7E-4959E40C78CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B86902-3751-4E17-8A2F-E2C6DF1EF6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="198">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
   <si>
     <t>Abzweigung Wanderweg</t>
   </si>
@@ -614,6 +614,12 @@
   </si>
   <si>
     <t>Grimsel Hospiz</t>
+  </si>
+  <si>
+    <t>First</t>
+  </si>
+  <si>
+    <t>Bachalpsee</t>
   </si>
 </sst>
 </file>
@@ -1426,7 +1432,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C196"/>
+  <dimension ref="A1:C198"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
@@ -2998,6 +3004,22 @@
         <v>1980</v>
       </c>
     </row>
+    <row r="197" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A197" t="s">
+        <v>198</v>
+      </c>
+      <c r="C197">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="198" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A198" t="s">
+        <v>199</v>
+      </c>
+      <c r="C198">
+        <v>2266</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C186">
     <sortCondition ref="A2:A186"/>

--- a/data/hm.xlsx
+++ b/data/hm.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\rufibach\90_github_repos\sport\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9B86902-3751-4E17-8A2F-E2C6DF1EF6F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D9F849F2-68F8-4410-8418-4812898C000B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="201">
   <si>
     <t>Abzweigung Wanderweg</t>
   </si>
@@ -620,6 +620,9 @@
   </si>
   <si>
     <t>Bachalpsee</t>
+  </si>
+  <si>
+    <t>Alpentower</t>
   </si>
 </sst>
 </file>
@@ -1432,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C198"/>
+  <dimension ref="A1:C199"/>
   <sheetFormatPr defaultColWidth="9.1796875" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="27.81640625" bestFit="1" customWidth="1"/>
@@ -3020,6 +3023,14 @@
         <v>2266</v>
       </c>
     </row>
+    <row r="199" spans="1:3" x14ac:dyDescent="0.35">
+      <c r="A199" t="s">
+        <v>200</v>
+      </c>
+      <c r="C199">
+        <v>2245</v>
+      </c>
+    </row>
   </sheetData>
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:C186">
     <sortCondition ref="A2:A186"/>
